--- a/utilities/variables.xlsx
+++ b/utilities/variables.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KDP_2023\CLEARS_EU\utilities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7DB2DB8-C9BC-4A6C-93C0-544BF3FC8C5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DEC2AE0-56DD-4F67-8443-ABC2C7E2F01B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{3966A5EA-18B5-40FC-82B6-8DC341B5B05B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{3966A5EA-18B5-40FC-82B6-8DC341B5B05B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$P$512</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$P$514</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1282" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1310" uniqueCount="245">
   <si>
     <t>Variable name</t>
   </si>
@@ -757,6 +757,21 @@
   </si>
   <si>
     <t>Power generation by technology</t>
+  </si>
+  <si>
+    <t>valley_h</t>
+  </si>
+  <si>
+    <t>Valley RLDC hours</t>
+  </si>
+  <si>
+    <t>Dynamic hourly electricity price by consumption band by country</t>
+  </si>
+  <si>
+    <t>dyn_elec_price</t>
+  </si>
+  <si>
+    <t>Calculated from Eurostat prices and Ember wholesale prices</t>
   </si>
 </sst>
 </file>
@@ -1631,25 +1646,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5694E675-77F6-4F54-A793-A54451BF0049}">
-  <dimension ref="A1:P501"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:P503"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="27.88671875" customWidth="1"/>
+    <col min="1" max="1" width="27.90625" customWidth="1"/>
     <col min="2" max="2" width="41" customWidth="1"/>
-    <col min="3" max="3" width="16.21875" customWidth="1"/>
-    <col min="4" max="4" width="15.77734375" customWidth="1"/>
-    <col min="5" max="5" width="19.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.5546875" customWidth="1"/>
-    <col min="7" max="10" width="9.21875" customWidth="1"/>
-    <col min="11" max="11" width="29.77734375" customWidth="1"/>
-    <col min="12" max="12" width="11.77734375" customWidth="1"/>
-    <col min="13" max="13" width="30.44140625" customWidth="1"/>
-    <col min="14" max="14" width="12.44140625" customWidth="1"/>
-    <col min="15" max="15" width="15.44140625" customWidth="1"/>
-    <col min="16" max="16" width="54.21875" customWidth="1"/>
+    <col min="3" max="3" width="16.1796875" customWidth="1"/>
+    <col min="4" max="4" width="15.81640625" customWidth="1"/>
+    <col min="5" max="5" width="19.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.54296875" customWidth="1"/>
+    <col min="7" max="10" width="9.1796875" customWidth="1"/>
+    <col min="11" max="11" width="29.81640625" customWidth="1"/>
+    <col min="12" max="12" width="11.81640625" customWidth="1"/>
+    <col min="13" max="13" width="30.453125" customWidth="1"/>
+    <col min="14" max="14" width="12.453125" customWidth="1"/>
+    <col min="15" max="15" width="15.453125" customWidth="1"/>
+    <col min="16" max="16" width="54.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1699,7 +1714,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>41</v>
       </c>
@@ -1746,7 +1761,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>156</v>
       </c>
@@ -1793,7 +1808,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>182</v>
       </c>
@@ -1840,7 +1855,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>53</v>
       </c>
@@ -1887,7 +1902,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>180</v>
       </c>
@@ -1934,7 +1949,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>42</v>
       </c>
@@ -1981,7 +1996,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>188</v>
       </c>
@@ -2028,7 +2043,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>56</v>
       </c>
@@ -2075,7 +2090,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>79</v>
       </c>
@@ -2122,7 +2137,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>175</v>
       </c>
@@ -2169,7 +2184,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>83</v>
       </c>
@@ -2216,7 +2231,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>82</v>
       </c>
@@ -2263,7 +2278,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>31</v>
       </c>
@@ -2310,7 +2325,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>174</v>
       </c>
@@ -2357,7 +2372,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>57</v>
       </c>
@@ -2404,7 +2419,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>50</v>
       </c>
@@ -2451,7 +2466,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>159</v>
       </c>
@@ -2498,7 +2513,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>184</v>
       </c>
@@ -2545,7 +2560,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>38</v>
       </c>
@@ -2592,7 +2607,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>192</v>
       </c>
@@ -2639,7 +2654,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>81</v>
       </c>
@@ -2686,7 +2701,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>121</v>
       </c>
@@ -2733,7 +2748,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>218</v>
       </c>
@@ -2780,7 +2795,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>123</v>
       </c>
@@ -2827,7 +2842,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>221</v>
       </c>
@@ -2874,7 +2889,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>117</v>
       </c>
@@ -2921,7 +2936,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>161</v>
       </c>
@@ -2968,7 +2983,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>48</v>
       </c>
@@ -3015,7 +3030,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>124</v>
       </c>
@@ -3062,7 +3077,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>122</v>
       </c>
@@ -3109,7 +3124,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>224</v>
       </c>
@@ -3156,7 +3171,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>118</v>
       </c>
@@ -3203,7 +3218,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>163</v>
       </c>
@@ -3250,12 +3265,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>132</v>
+        <v>243</v>
       </c>
       <c r="B35" t="s">
-        <v>133</v>
+        <v>242</v>
       </c>
       <c r="C35" t="s">
         <v>138</v>
@@ -3279,16 +3294,16 @@
         <v>10</v>
       </c>
       <c r="J35" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="K35" t="s">
         <v>16</v>
       </c>
       <c r="L35">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="M35" t="s">
-        <v>134</v>
+        <v>244</v>
       </c>
       <c r="N35" t="s">
         <v>7</v>
@@ -3297,21 +3312,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>235</v>
+        <v>132</v>
       </c>
       <c r="B36" t="s">
-        <v>236</v>
+        <v>133</v>
       </c>
       <c r="C36" t="s">
-        <v>237</v>
+        <v>138</v>
       </c>
       <c r="D36" t="s">
-        <v>238</v>
+        <v>89</v>
       </c>
       <c r="E36" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="F36" t="s">
         <v>10</v>
@@ -3335,7 +3350,7 @@
         <v>2024</v>
       </c>
       <c r="M36" t="s">
-        <v>27</v>
+        <v>134</v>
       </c>
       <c r="N36" t="s">
         <v>7</v>
@@ -3344,18 +3359,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>198</v>
+        <v>235</v>
       </c>
       <c r="B37" t="s">
-        <v>199</v>
+        <v>236</v>
       </c>
       <c r="C37" t="s">
-        <v>158</v>
+        <v>237</v>
       </c>
       <c r="D37" t="s">
-        <v>89</v>
+        <v>238</v>
       </c>
       <c r="E37" t="s">
         <v>10</v>
@@ -3373,16 +3388,16 @@
         <v>10</v>
       </c>
       <c r="J37" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="K37" t="s">
-        <v>14</v>
-      </c>
-      <c r="L37" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="L37">
+        <v>2024</v>
       </c>
       <c r="M37" t="s">
-        <v>200</v>
+        <v>27</v>
       </c>
       <c r="N37" t="s">
         <v>7</v>
@@ -3391,18 +3406,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B38" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C38" t="s">
-        <v>212</v>
+        <v>158</v>
       </c>
       <c r="D38" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="E38" t="s">
         <v>10</v>
@@ -3414,22 +3429,22 @@
         <v>10</v>
       </c>
       <c r="H38" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I38" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="J38" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="K38" t="s">
         <v>14</v>
       </c>
-      <c r="L38">
-        <v>2022</v>
+      <c r="L38" t="s">
+        <v>15</v>
       </c>
       <c r="M38" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="N38" t="s">
         <v>7</v>
@@ -3438,18 +3453,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="B39" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="C39" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D39" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="E39" t="s">
         <v>10</v>
@@ -3461,13 +3476,13 @@
         <v>10</v>
       </c>
       <c r="H39" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I39" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="J39" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="K39" t="s">
         <v>14</v>
@@ -3476,7 +3491,7 @@
         <v>2022</v>
       </c>
       <c r="M39" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="N39" t="s">
         <v>7</v>
@@ -3485,15 +3500,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>136</v>
+        <v>208</v>
       </c>
       <c r="B40" t="s">
-        <v>137</v>
+        <v>209</v>
       </c>
       <c r="C40" t="s">
-        <v>138</v>
+        <v>210</v>
       </c>
       <c r="D40" t="s">
         <v>89</v>
@@ -3514,16 +3529,16 @@
         <v>10</v>
       </c>
       <c r="J40" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="K40" t="s">
         <v>14</v>
       </c>
       <c r="L40">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="M40" t="s">
-        <v>61</v>
+        <v>211</v>
       </c>
       <c r="N40" t="s">
         <v>7</v>
@@ -3532,15 +3547,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="B41" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="C41" t="s">
-        <v>63</v>
+        <v>138</v>
       </c>
       <c r="D41" t="s">
         <v>89</v>
@@ -3564,13 +3579,13 @@
         <v>10</v>
       </c>
       <c r="K41" t="s">
-        <v>33</v>
-      </c>
-      <c r="L41" t="s">
-        <v>15</v>
+        <v>14</v>
+      </c>
+      <c r="L41">
+        <v>2024</v>
       </c>
       <c r="M41" t="s">
-        <v>154</v>
+        <v>61</v>
       </c>
       <c r="N41" t="s">
         <v>7</v>
@@ -3579,21 +3594,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>238</v>
+        <v>152</v>
       </c>
       <c r="B42" t="s">
-        <v>239</v>
+        <v>153</v>
       </c>
       <c r="C42" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D42" t="s">
         <v>89</v>
       </c>
       <c r="E42" t="s">
-        <v>238</v>
+        <v>10</v>
       </c>
       <c r="F42" t="s">
         <v>10</v>
@@ -3605,19 +3620,19 @@
         <v>10</v>
       </c>
       <c r="I42" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J42" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="K42" t="s">
-        <v>16</v>
-      </c>
-      <c r="L42">
-        <v>2024</v>
+        <v>33</v>
+      </c>
+      <c r="L42" t="s">
+        <v>15</v>
       </c>
       <c r="M42" t="s">
-        <v>232</v>
+        <v>154</v>
       </c>
       <c r="N42" t="s">
         <v>7</v>
@@ -3626,74 +3641,74 @@
         <v>12</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
+        <v>238</v>
+      </c>
+      <c r="B43" t="s">
+        <v>239</v>
+      </c>
+      <c r="C43" t="s">
+        <v>59</v>
+      </c>
+      <c r="D43" t="s">
+        <v>89</v>
+      </c>
+      <c r="E43" t="s">
+        <v>238</v>
+      </c>
+      <c r="F43" t="s">
+        <v>10</v>
+      </c>
+      <c r="G43" t="s">
+        <v>10</v>
+      </c>
+      <c r="H43" t="s">
+        <v>10</v>
+      </c>
+      <c r="I43" t="s">
+        <v>20</v>
+      </c>
+      <c r="J43" t="s">
+        <v>21</v>
+      </c>
+      <c r="K43" t="s">
+        <v>16</v>
+      </c>
+      <c r="L43">
+        <v>2024</v>
+      </c>
+      <c r="M43" t="s">
+        <v>232</v>
+      </c>
+      <c r="N43" t="s">
+        <v>7</v>
+      </c>
+      <c r="O43" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
         <v>104</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B44" t="s">
         <v>145</v>
       </c>
-      <c r="C43" t="s">
-        <v>15</v>
-      </c>
-      <c r="D43" t="s">
-        <v>89</v>
-      </c>
-      <c r="E43" t="s">
+      <c r="C44" t="s">
+        <v>15</v>
+      </c>
+      <c r="D44" t="s">
+        <v>89</v>
+      </c>
+      <c r="E44" t="s">
         <v>22</v>
       </c>
-      <c r="F43" t="s">
+      <c r="F44" t="s">
         <v>55</v>
       </c>
-      <c r="G43" t="s">
+      <c r="G44" t="s">
         <v>173</v>
-      </c>
-      <c r="H43" t="s">
-        <v>10</v>
-      </c>
-      <c r="I43" t="s">
-        <v>10</v>
-      </c>
-      <c r="J43" t="s">
-        <v>10</v>
-      </c>
-      <c r="K43" t="s">
-        <v>14</v>
-      </c>
-      <c r="L43" t="s">
-        <v>15</v>
-      </c>
-      <c r="M43" t="s">
-        <v>15</v>
-      </c>
-      <c r="N43" t="s">
-        <v>7</v>
-      </c>
-      <c r="O43" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>99</v>
-      </c>
-      <c r="B44" t="s">
-        <v>100</v>
-      </c>
-      <c r="C44" t="s">
-        <v>101</v>
-      </c>
-      <c r="D44" t="s">
-        <v>89</v>
-      </c>
-      <c r="E44" t="s">
-        <v>10</v>
-      </c>
-      <c r="F44" t="s">
-        <v>10</v>
-      </c>
-      <c r="G44" t="s">
-        <v>10</v>
       </c>
       <c r="H44" t="s">
         <v>10</v>
@@ -3707,28 +3722,28 @@
       <c r="K44" t="s">
         <v>14</v>
       </c>
-      <c r="L44">
-        <v>2024</v>
+      <c r="L44" t="s">
+        <v>15</v>
       </c>
       <c r="M44" t="s">
-        <v>103</v>
+        <v>15</v>
       </c>
       <c r="N44" t="s">
         <v>7</v>
       </c>
       <c r="O44" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>144</v>
+        <v>99</v>
       </c>
       <c r="B45" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C45" t="s">
-        <v>15</v>
+        <v>101</v>
       </c>
       <c r="D45" t="s">
         <v>89</v>
@@ -3758,7 +3773,7 @@
         <v>2024</v>
       </c>
       <c r="M45" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N45" t="s">
         <v>7</v>
@@ -3767,153 +3782,153 @@
         <v>12</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
+        <v>144</v>
+      </c>
+      <c r="B46" t="s">
+        <v>98</v>
+      </c>
+      <c r="C46" t="s">
+        <v>15</v>
+      </c>
+      <c r="D46" t="s">
+        <v>89</v>
+      </c>
+      <c r="E46" t="s">
+        <v>10</v>
+      </c>
+      <c r="F46" t="s">
+        <v>10</v>
+      </c>
+      <c r="G46" t="s">
+        <v>10</v>
+      </c>
+      <c r="H46" t="s">
+        <v>10</v>
+      </c>
+      <c r="I46" t="s">
+        <v>10</v>
+      </c>
+      <c r="J46" t="s">
+        <v>10</v>
+      </c>
+      <c r="K46" t="s">
+        <v>14</v>
+      </c>
+      <c r="L46">
+        <v>2024</v>
+      </c>
+      <c r="M46" t="s">
+        <v>102</v>
+      </c>
+      <c r="N46" t="s">
+        <v>7</v>
+      </c>
+      <c r="O46" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
         <v>201</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B47" t="s">
         <v>202</v>
       </c>
-      <c r="C46" t="s">
-        <v>15</v>
-      </c>
-      <c r="D46" t="s">
-        <v>89</v>
-      </c>
-      <c r="E46" t="s">
+      <c r="C47" t="s">
+        <v>15</v>
+      </c>
+      <c r="D47" t="s">
+        <v>89</v>
+      </c>
+      <c r="E47" t="s">
         <v>203</v>
       </c>
-      <c r="F46" t="s">
-        <v>10</v>
-      </c>
-      <c r="G46" t="s">
-        <v>10</v>
-      </c>
-      <c r="H46" t="s">
-        <v>10</v>
-      </c>
-      <c r="I46" t="s">
-        <v>10</v>
-      </c>
-      <c r="J46" t="s">
+      <c r="F47" t="s">
+        <v>10</v>
+      </c>
+      <c r="G47" t="s">
+        <v>10</v>
+      </c>
+      <c r="H47" t="s">
+        <v>10</v>
+      </c>
+      <c r="I47" t="s">
+        <v>10</v>
+      </c>
+      <c r="J47" t="s">
         <v>30</v>
       </c>
-      <c r="K46" t="s">
+      <c r="K47" t="s">
         <v>16</v>
       </c>
-      <c r="L46" t="s">
-        <v>15</v>
-      </c>
-      <c r="M46" t="s">
-        <v>15</v>
-      </c>
-      <c r="N46" t="s">
-        <v>7</v>
-      </c>
-      <c r="O46" t="s">
+      <c r="L47" t="s">
+        <v>15</v>
+      </c>
+      <c r="M47" t="s">
+        <v>15</v>
+      </c>
+      <c r="N47" t="s">
+        <v>7</v>
+      </c>
+      <c r="O47" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
         <v>107</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B48" t="s">
         <v>108</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C48" t="s">
         <v>63</v>
       </c>
-      <c r="D47" t="s">
-        <v>89</v>
-      </c>
-      <c r="E47" t="s">
-        <v>10</v>
-      </c>
-      <c r="F47" t="s">
-        <v>10</v>
-      </c>
-      <c r="G47" t="s">
-        <v>10</v>
-      </c>
-      <c r="H47" t="s">
-        <v>10</v>
-      </c>
-      <c r="I47" t="s">
-        <v>10</v>
-      </c>
-      <c r="J47" t="s">
-        <v>10</v>
-      </c>
-      <c r="K47" t="s">
+      <c r="D48" t="s">
+        <v>89</v>
+      </c>
+      <c r="E48" t="s">
+        <v>10</v>
+      </c>
+      <c r="F48" t="s">
+        <v>10</v>
+      </c>
+      <c r="G48" t="s">
+        <v>10</v>
+      </c>
+      <c r="H48" t="s">
+        <v>10</v>
+      </c>
+      <c r="I48" t="s">
+        <v>10</v>
+      </c>
+      <c r="J48" t="s">
+        <v>10</v>
+      </c>
+      <c r="K48" t="s">
         <v>33</v>
       </c>
-      <c r="L47">
+      <c r="L48">
         <v>2024</v>
       </c>
-      <c r="M47" t="s">
+      <c r="M48" t="s">
         <v>109</v>
       </c>
-      <c r="N47" t="s">
-        <v>7</v>
-      </c>
-      <c r="O47" t="s">
+      <c r="N48" t="s">
+        <v>7</v>
+      </c>
+      <c r="O48" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
         <v>228</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B49" t="s">
         <v>230</v>
-      </c>
-      <c r="C48" t="s">
-        <v>59</v>
-      </c>
-      <c r="D48" t="s">
-        <v>89</v>
-      </c>
-      <c r="E48" t="s">
-        <v>10</v>
-      </c>
-      <c r="F48" t="s">
-        <v>10</v>
-      </c>
-      <c r="G48" t="s">
-        <v>10</v>
-      </c>
-      <c r="H48" t="s">
-        <v>20</v>
-      </c>
-      <c r="I48" t="s">
-        <v>21</v>
-      </c>
-      <c r="J48" t="s">
-        <v>30</v>
-      </c>
-      <c r="K48" t="s">
-        <v>16</v>
-      </c>
-      <c r="L48" t="s">
-        <v>15</v>
-      </c>
-      <c r="M48" t="s">
-        <v>15</v>
-      </c>
-      <c r="N48" t="s">
-        <v>7</v>
-      </c>
-      <c r="O48" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>229</v>
-      </c>
-      <c r="B49" t="s">
-        <v>231</v>
       </c>
       <c r="C49" t="s">
         <v>59</v>
@@ -3955,12 +3970,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>58</v>
+        <v>229</v>
       </c>
       <c r="B50" t="s">
-        <v>172</v>
+        <v>231</v>
       </c>
       <c r="C50" t="s">
         <v>59</v>
@@ -3978,13 +3993,13 @@
         <v>10</v>
       </c>
       <c r="H50" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I50" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J50" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="K50" t="s">
         <v>16</v>
@@ -3993,21 +4008,21 @@
         <v>15</v>
       </c>
       <c r="M50" t="s">
-        <v>232</v>
+        <v>15</v>
       </c>
       <c r="N50" t="s">
         <v>7</v>
       </c>
       <c r="O50" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>233</v>
+        <v>58</v>
       </c>
       <c r="B51" t="s">
-        <v>234</v>
+        <v>172</v>
       </c>
       <c r="C51" t="s">
         <v>59</v>
@@ -4049,15 +4064,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>205</v>
+        <v>233</v>
       </c>
       <c r="B52" t="s">
-        <v>206</v>
+        <v>234</v>
       </c>
       <c r="C52" t="s">
-        <v>207</v>
+        <v>59</v>
       </c>
       <c r="D52" t="s">
         <v>89</v>
@@ -4075,19 +4090,19 @@
         <v>10</v>
       </c>
       <c r="I52" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J52" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="K52" t="s">
         <v>16</v>
       </c>
-      <c r="L52">
-        <v>2022</v>
+      <c r="L52" t="s">
+        <v>15</v>
       </c>
       <c r="M52" t="s">
-        <v>204</v>
+        <v>232</v>
       </c>
       <c r="N52" t="s">
         <v>7</v>
@@ -4096,15 +4111,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>150</v>
+        <v>205</v>
       </c>
       <c r="B53" t="s">
-        <v>151</v>
+        <v>206</v>
       </c>
       <c r="C53" t="s">
-        <v>101</v>
+        <v>207</v>
       </c>
       <c r="D53" t="s">
         <v>89</v>
@@ -4125,16 +4140,16 @@
         <v>10</v>
       </c>
       <c r="J53" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="K53" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L53">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="M53" t="s">
-        <v>134</v>
+        <v>204</v>
       </c>
       <c r="N53" t="s">
         <v>7</v>
@@ -4143,24 +4158,24 @@
         <v>12</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>213</v>
+        <v>150</v>
       </c>
       <c r="B54" t="s">
-        <v>214</v>
+        <v>151</v>
       </c>
       <c r="C54" t="s">
-        <v>15</v>
+        <v>101</v>
       </c>
       <c r="D54" t="s">
         <v>89</v>
       </c>
       <c r="E54" t="s">
-        <v>213</v>
+        <v>10</v>
       </c>
       <c r="F54" t="s">
-        <v>227</v>
+        <v>10</v>
       </c>
       <c r="G54" t="s">
         <v>10</v>
@@ -4172,16 +4187,16 @@
         <v>10</v>
       </c>
       <c r="J54" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="K54" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L54">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="M54" t="s">
-        <v>215</v>
+        <v>134</v>
       </c>
       <c r="N54" t="s">
         <v>7</v>
@@ -4190,24 +4205,24 @@
         <v>12</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B55" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C55" t="s">
-        <v>101</v>
+        <v>15</v>
       </c>
       <c r="D55" t="s">
         <v>89</v>
       </c>
       <c r="E55" t="s">
-        <v>10</v>
+        <v>213</v>
       </c>
       <c r="F55" t="s">
-        <v>10</v>
+        <v>227</v>
       </c>
       <c r="G55" t="s">
         <v>10</v>
@@ -4222,13 +4237,13 @@
         <v>30</v>
       </c>
       <c r="K55" t="s">
-        <v>14</v>
-      </c>
-      <c r="L55" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="L55">
+        <v>2024</v>
       </c>
       <c r="M55" t="s">
-        <v>154</v>
+        <v>215</v>
       </c>
       <c r="N55" t="s">
         <v>7</v>
@@ -4237,12 +4252,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>45</v>
+        <v>240</v>
       </c>
       <c r="B56" t="s">
-        <v>68</v>
+        <v>241</v>
       </c>
       <c r="C56" t="s">
         <v>15</v>
@@ -4251,13 +4266,13 @@
         <v>89</v>
       </c>
       <c r="E56" t="s">
-        <v>22</v>
+        <v>213</v>
       </c>
       <c r="F56" t="s">
-        <v>55</v>
+        <v>227</v>
       </c>
       <c r="G56" t="s">
-        <v>173</v>
+        <v>10</v>
       </c>
       <c r="H56" t="s">
         <v>10</v>
@@ -4269,36 +4284,36 @@
         <v>30</v>
       </c>
       <c r="K56" t="s">
-        <v>54</v>
-      </c>
-      <c r="L56" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="L56">
+        <v>2024</v>
       </c>
       <c r="M56" t="s">
-        <v>15</v>
+        <v>215</v>
       </c>
       <c r="N56" t="s">
         <v>7</v>
       </c>
       <c r="O56" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>40</v>
+        <v>216</v>
       </c>
       <c r="B57" t="s">
-        <v>88</v>
+        <v>217</v>
       </c>
       <c r="C57" t="s">
-        <v>15</v>
+        <v>101</v>
       </c>
       <c r="D57" t="s">
         <v>89</v>
       </c>
       <c r="E57" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F57" t="s">
         <v>10</v>
@@ -4313,16 +4328,16 @@
         <v>10</v>
       </c>
       <c r="J57" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="K57" t="s">
         <v>14</v>
       </c>
-      <c r="L57">
-        <v>2011</v>
+      <c r="L57" t="s">
+        <v>15</v>
       </c>
       <c r="M57" t="s">
-        <v>39</v>
+        <v>154</v>
       </c>
       <c r="N57" t="s">
         <v>7</v>
@@ -4331,12 +4346,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="B58" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="C58" t="s">
         <v>15</v>
@@ -4348,45 +4363,45 @@
         <v>22</v>
       </c>
       <c r="F58" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="G58" t="s">
-        <v>10</v>
+        <v>173</v>
       </c>
       <c r="H58" t="s">
         <v>10</v>
       </c>
       <c r="I58" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J58" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="K58" t="s">
-        <v>14</v>
-      </c>
-      <c r="L58">
-        <v>2022</v>
+        <v>54</v>
+      </c>
+      <c r="L58" t="s">
+        <v>15</v>
       </c>
       <c r="M58" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="N58" t="s">
         <v>7</v>
       </c>
       <c r="O58" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>128</v>
+        <v>40</v>
       </c>
       <c r="B59" t="s">
-        <v>129</v>
+        <v>88</v>
       </c>
       <c r="C59" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="D59" t="s">
         <v>89</v>
@@ -4395,45 +4410,45 @@
         <v>22</v>
       </c>
       <c r="F59" t="s">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="G59" t="s">
-        <v>173</v>
+        <v>10</v>
       </c>
       <c r="H59" t="s">
         <v>10</v>
       </c>
       <c r="I59" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J59" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="K59" t="s">
         <v>14</v>
       </c>
-      <c r="L59" t="s">
-        <v>15</v>
+      <c r="L59">
+        <v>2011</v>
       </c>
       <c r="M59" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="N59" t="s">
         <v>7</v>
       </c>
       <c r="O59" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="B60" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="C60" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="D60" t="s">
         <v>89</v>
@@ -4442,107 +4457,107 @@
         <v>22</v>
       </c>
       <c r="F60" t="s">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="G60" t="s">
-        <v>173</v>
+        <v>10</v>
       </c>
       <c r="H60" t="s">
         <v>10</v>
       </c>
       <c r="I60" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J60" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="K60" t="s">
         <v>14</v>
       </c>
-      <c r="L60" t="s">
-        <v>15</v>
+      <c r="L60">
+        <v>2022</v>
       </c>
       <c r="M60" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="N60" t="s">
         <v>7</v>
       </c>
       <c r="O60" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>128</v>
+      </c>
+      <c r="B61" t="s">
+        <v>129</v>
+      </c>
+      <c r="C61" t="s">
+        <v>26</v>
+      </c>
+      <c r="D61" t="s">
+        <v>89</v>
+      </c>
+      <c r="E61" t="s">
+        <v>22</v>
+      </c>
+      <c r="F61" t="s">
+        <v>55</v>
+      </c>
+      <c r="G61" t="s">
+        <v>173</v>
+      </c>
+      <c r="H61" t="s">
+        <v>10</v>
+      </c>
+      <c r="I61" t="s">
+        <v>20</v>
+      </c>
+      <c r="J61" t="s">
+        <v>21</v>
+      </c>
+      <c r="K61" t="s">
+        <v>14</v>
+      </c>
+      <c r="L61" t="s">
+        <v>15</v>
+      </c>
+      <c r="M61" t="s">
+        <v>15</v>
+      </c>
+      <c r="N61" t="s">
+        <v>7</v>
+      </c>
+      <c r="O61" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>149</v>
-      </c>
-      <c r="B61" t="s">
-        <v>135</v>
-      </c>
-      <c r="C61" t="s">
-        <v>59</v>
-      </c>
-      <c r="D61" t="s">
-        <v>89</v>
-      </c>
-      <c r="E61" t="s">
-        <v>10</v>
-      </c>
-      <c r="F61" t="s">
-        <v>10</v>
-      </c>
-      <c r="G61" t="s">
-        <v>10</v>
-      </c>
-      <c r="H61" t="s">
-        <v>10</v>
-      </c>
-      <c r="I61" t="s">
-        <v>10</v>
-      </c>
-      <c r="J61" t="s">
-        <v>30</v>
-      </c>
-      <c r="K61" t="s">
-        <v>16</v>
-      </c>
-      <c r="L61">
-        <v>2024</v>
-      </c>
-      <c r="M61" t="s">
-        <v>111</v>
-      </c>
-      <c r="N61" t="s">
-        <v>7</v>
-      </c>
-      <c r="O61" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>168</v>
+        <v>75</v>
       </c>
       <c r="B62" t="s">
-        <v>169</v>
+        <v>66</v>
       </c>
       <c r="C62" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D62" t="s">
         <v>89</v>
       </c>
       <c r="E62" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F62" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="G62" t="s">
-        <v>10</v>
+        <v>173</v>
       </c>
       <c r="H62" t="s">
-        <v>155</v>
+        <v>10</v>
       </c>
       <c r="I62" t="s">
         <v>10</v>
@@ -4551,7 +4566,7 @@
         <v>30</v>
       </c>
       <c r="K62" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L62" t="s">
         <v>15</v>
@@ -4566,30 +4581,30 @@
         <v>29</v>
       </c>
     </row>
-    <row r="63" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="B63" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="C63" t="s">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="D63" t="s">
         <v>89</v>
       </c>
       <c r="E63" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F63" t="s">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="G63" t="s">
-        <v>173</v>
+        <v>10</v>
       </c>
       <c r="H63" t="s">
-        <v>155</v>
+        <v>10</v>
       </c>
       <c r="I63" t="s">
         <v>10</v>
@@ -4598,78 +4613,77 @@
         <v>30</v>
       </c>
       <c r="K63" t="s">
-        <v>54</v>
-      </c>
-      <c r="L63" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="L63">
+        <v>2024</v>
       </c>
       <c r="M63" t="s">
-        <v>15</v>
+        <v>111</v>
       </c>
       <c r="N63" t="s">
         <v>7</v>
       </c>
       <c r="O63" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>168</v>
+      </c>
+      <c r="B64" t="s">
+        <v>169</v>
+      </c>
+      <c r="C64" t="s">
+        <v>59</v>
+      </c>
+      <c r="D64" t="s">
+        <v>89</v>
+      </c>
+      <c r="E64" t="s">
+        <v>10</v>
+      </c>
+      <c r="F64" t="s">
+        <v>10</v>
+      </c>
+      <c r="G64" t="s">
+        <v>10</v>
+      </c>
+      <c r="H64" t="s">
+        <v>155</v>
+      </c>
+      <c r="I64" t="s">
+        <v>10</v>
+      </c>
+      <c r="J64" t="s">
+        <v>30</v>
+      </c>
+      <c r="K64" t="s">
+        <v>16</v>
+      </c>
+      <c r="L64" t="s">
+        <v>15</v>
+      </c>
+      <c r="M64" t="s">
+        <v>15</v>
+      </c>
+      <c r="N64" t="s">
+        <v>7</v>
+      </c>
+      <c r="O64" t="s">
         <v>29</v>
       </c>
-      <c r="P63"/>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
-        <v>25</v>
-      </c>
-      <c r="B64" t="s">
-        <v>90</v>
-      </c>
-      <c r="C64" t="s">
-        <v>26</v>
-      </c>
-      <c r="D64" t="s">
-        <v>89</v>
-      </c>
-      <c r="E64" t="s">
-        <v>10</v>
-      </c>
-      <c r="F64" t="s">
-        <v>10</v>
-      </c>
-      <c r="G64" t="s">
-        <v>173</v>
-      </c>
-      <c r="H64" t="s">
-        <v>10</v>
-      </c>
-      <c r="I64" t="s">
-        <v>20</v>
-      </c>
-      <c r="J64" t="s">
-        <v>21</v>
-      </c>
-      <c r="K64" t="s">
-        <v>14</v>
-      </c>
-      <c r="L64">
-        <v>2020</v>
-      </c>
-      <c r="M64" t="s">
-        <v>27</v>
-      </c>
-      <c r="N64" t="s">
-        <v>7</v>
-      </c>
-      <c r="O64" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="65" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>130</v>
+        <v>73</v>
       </c>
       <c r="B65" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="C65" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="D65" t="s">
         <v>89</v>
@@ -4684,16 +4698,16 @@
         <v>173</v>
       </c>
       <c r="H65" t="s">
-        <v>10</v>
+        <v>155</v>
       </c>
       <c r="I65" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J65" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="K65" t="s">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="L65" t="s">
         <v>15</v>
@@ -4707,10 +4721,11 @@
       <c r="O65" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P65"/>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>167</v>
+        <v>25</v>
       </c>
       <c r="B66" t="s">
         <v>90</v>
@@ -4722,45 +4737,45 @@
         <v>89</v>
       </c>
       <c r="E66" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F66" t="s">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="G66" t="s">
         <v>173</v>
       </c>
       <c r="H66" t="s">
+        <v>10</v>
+      </c>
+      <c r="I66" t="s">
         <v>20</v>
       </c>
-      <c r="I66" t="s">
+      <c r="J66" t="s">
         <v>21</v>
       </c>
-      <c r="J66" t="s">
-        <v>30</v>
-      </c>
       <c r="K66" t="s">
-        <v>16</v>
-      </c>
-      <c r="L66" t="s">
-        <v>15</v>
+        <v>14</v>
+      </c>
+      <c r="L66">
+        <v>2023</v>
       </c>
       <c r="M66" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="N66" t="s">
         <v>7</v>
       </c>
       <c r="O66" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>165</v>
+        <v>130</v>
       </c>
       <c r="B67" t="s">
-        <v>166</v>
+        <v>131</v>
       </c>
       <c r="C67" t="s">
         <v>26</v>
@@ -4778,16 +4793,16 @@
         <v>173</v>
       </c>
       <c r="H67" t="s">
+        <v>10</v>
+      </c>
+      <c r="I67" t="s">
         <v>20</v>
       </c>
-      <c r="I67" t="s">
+      <c r="J67" t="s">
         <v>21</v>
       </c>
-      <c r="J67" t="s">
-        <v>155</v>
-      </c>
       <c r="K67" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L67" t="s">
         <v>15</v>
@@ -4802,62 +4817,62 @@
         <v>29</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>110</v>
+        <v>167</v>
       </c>
       <c r="B68" t="s">
-        <v>135</v>
+        <v>90</v>
       </c>
       <c r="C68" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D68" t="s">
         <v>89</v>
       </c>
       <c r="E68" t="s">
-        <v>112</v>
+        <v>22</v>
       </c>
       <c r="F68" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="G68" t="s">
-        <v>10</v>
+        <v>173</v>
       </c>
       <c r="H68" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I68" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="J68" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="K68" t="s">
         <v>16</v>
       </c>
-      <c r="L68">
-        <v>2024</v>
+      <c r="L68" t="s">
+        <v>15</v>
       </c>
       <c r="M68" t="s">
-        <v>111</v>
+        <v>15</v>
       </c>
       <c r="N68" t="s">
         <v>7</v>
       </c>
       <c r="O68" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>76</v>
+        <v>165</v>
       </c>
       <c r="B69" t="s">
-        <v>67</v>
+        <v>166</v>
       </c>
       <c r="C69" t="s">
-        <v>63</v>
+        <v>26</v>
       </c>
       <c r="D69" t="s">
         <v>89</v>
@@ -4872,16 +4887,16 @@
         <v>173</v>
       </c>
       <c r="H69" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I69" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="J69" t="s">
-        <v>30</v>
+        <v>155</v>
       </c>
       <c r="K69" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L69" t="s">
         <v>15</v>
@@ -4896,12 +4911,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>71</v>
+        <v>110</v>
       </c>
       <c r="B70" t="s">
-        <v>94</v>
+        <v>135</v>
       </c>
       <c r="C70" t="s">
         <v>15</v>
@@ -4910,45 +4925,45 @@
         <v>89</v>
       </c>
       <c r="E70" t="s">
-        <v>22</v>
+        <v>112</v>
       </c>
       <c r="F70" t="s">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="G70" t="s">
-        <v>173</v>
+        <v>10</v>
       </c>
       <c r="H70" t="s">
-        <v>155</v>
+        <v>10</v>
       </c>
       <c r="I70" t="s">
         <v>10</v>
       </c>
       <c r="J70" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="K70" t="s">
-        <v>54</v>
-      </c>
-      <c r="L70" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="L70">
+        <v>2024</v>
       </c>
       <c r="M70" t="s">
-        <v>15</v>
+        <v>111</v>
       </c>
       <c r="N70" t="s">
         <v>7</v>
       </c>
       <c r="O70" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B71" t="s">
-        <v>93</v>
+        <v>67</v>
       </c>
       <c r="C71" t="s">
         <v>63</v>
@@ -4990,15 +5005,15 @@
         <v>29</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C72" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="D72" t="s">
         <v>89</v>
@@ -5013,16 +5028,16 @@
         <v>173</v>
       </c>
       <c r="H72" t="s">
-        <v>10</v>
+        <v>155</v>
       </c>
       <c r="I72" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J72" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="K72" t="s">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="L72" t="s">
         <v>15</v>
@@ -5037,27 +5052,27 @@
         <v>29</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>176</v>
+        <v>78</v>
       </c>
       <c r="B73" t="s">
-        <v>177</v>
+        <v>93</v>
       </c>
       <c r="C73" t="s">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="D73" t="s">
         <v>89</v>
       </c>
       <c r="E73" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F73" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="G73" t="s">
-        <v>10</v>
+        <v>173</v>
       </c>
       <c r="H73" t="s">
         <v>10</v>
@@ -5066,33 +5081,33 @@
         <v>10</v>
       </c>
       <c r="J73" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="K73" t="s">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="L73" t="s">
         <v>15</v>
       </c>
       <c r="M73" t="s">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="N73" t="s">
         <v>7</v>
       </c>
       <c r="O73" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>85</v>
+        <v>28</v>
       </c>
       <c r="B74" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C74" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D74" t="s">
         <v>89</v>
@@ -5110,13 +5125,13 @@
         <v>10</v>
       </c>
       <c r="I74" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J74" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="K74" t="s">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="L74" t="s">
         <v>15</v>
@@ -5131,12 +5146,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>84</v>
+        <v>176</v>
       </c>
       <c r="B75" t="s">
-        <v>86</v>
+        <v>177</v>
       </c>
       <c r="C75" t="s">
         <v>15</v>
@@ -5145,13 +5160,13 @@
         <v>89</v>
       </c>
       <c r="E75" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F75" t="s">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="G75" t="s">
-        <v>173</v>
+        <v>10</v>
       </c>
       <c r="H75" t="s">
         <v>10</v>
@@ -5160,7 +5175,7 @@
         <v>10</v>
       </c>
       <c r="J75" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="K75" t="s">
         <v>54</v>
@@ -5169,36 +5184,36 @@
         <v>15</v>
       </c>
       <c r="M75" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="N75" t="s">
         <v>7</v>
       </c>
       <c r="O75" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="B76" t="s">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="C76" t="s">
         <v>15</v>
       </c>
       <c r="D76" t="s">
-        <v>35</v>
+        <v>89</v>
       </c>
       <c r="E76" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F76" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="G76" t="s">
-        <v>10</v>
+        <v>173</v>
       </c>
       <c r="H76" t="s">
         <v>10</v>
@@ -5210,7 +5225,7 @@
         <v>30</v>
       </c>
       <c r="K76" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="L76" t="s">
         <v>15</v>
@@ -5222,15 +5237,15 @@
         <v>7</v>
       </c>
       <c r="O76" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>178</v>
+        <v>84</v>
       </c>
       <c r="B77" t="s">
-        <v>179</v>
+        <v>86</v>
       </c>
       <c r="C77" t="s">
         <v>15</v>
@@ -5239,13 +5254,13 @@
         <v>89</v>
       </c>
       <c r="E77" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F77" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="G77" t="s">
-        <v>10</v>
+        <v>173</v>
       </c>
       <c r="H77" t="s">
         <v>10</v>
@@ -5254,7 +5269,7 @@
         <v>10</v>
       </c>
       <c r="J77" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="K77" t="s">
         <v>54</v>
@@ -5263,36 +5278,36 @@
         <v>15</v>
       </c>
       <c r="M77" t="s">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="N77" t="s">
         <v>7</v>
       </c>
       <c r="O77" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B78" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="C78" t="s">
         <v>15</v>
       </c>
       <c r="D78" t="s">
-        <v>89</v>
+        <v>35</v>
       </c>
       <c r="E78" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F78" t="s">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="G78" t="s">
-        <v>173</v>
+        <v>10</v>
       </c>
       <c r="H78" t="s">
         <v>10</v>
@@ -5304,7 +5319,7 @@
         <v>30</v>
       </c>
       <c r="K78" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="L78" t="s">
         <v>15</v>
@@ -5316,15 +5331,15 @@
         <v>7</v>
       </c>
       <c r="O78" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>74</v>
+        <v>178</v>
       </c>
       <c r="B79" t="s">
-        <v>97</v>
+        <v>179</v>
       </c>
       <c r="C79" t="s">
         <v>15</v>
@@ -5333,22 +5348,22 @@
         <v>89</v>
       </c>
       <c r="E79" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F79" t="s">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="G79" t="s">
-        <v>173</v>
+        <v>10</v>
       </c>
       <c r="H79" t="s">
-        <v>155</v>
+        <v>10</v>
       </c>
       <c r="I79" t="s">
         <v>10</v>
       </c>
       <c r="J79" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="K79" t="s">
         <v>54</v>
@@ -5357,71 +5372,71 @@
         <v>15</v>
       </c>
       <c r="M79" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="N79" t="s">
         <v>7</v>
       </c>
       <c r="O79" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>72</v>
+      </c>
+      <c r="B80" t="s">
+        <v>95</v>
+      </c>
+      <c r="C80" t="s">
+        <v>15</v>
+      </c>
+      <c r="D80" t="s">
+        <v>89</v>
+      </c>
+      <c r="E80" t="s">
+        <v>22</v>
+      </c>
+      <c r="F80" t="s">
+        <v>55</v>
+      </c>
+      <c r="G80" t="s">
+        <v>173</v>
+      </c>
+      <c r="H80" t="s">
+        <v>10</v>
+      </c>
+      <c r="I80" t="s">
+        <v>10</v>
+      </c>
+      <c r="J80" t="s">
+        <v>30</v>
+      </c>
+      <c r="K80" t="s">
+        <v>54</v>
+      </c>
+      <c r="L80" t="s">
+        <v>15</v>
+      </c>
+      <c r="M80" t="s">
+        <v>15</v>
+      </c>
+      <c r="N80" t="s">
+        <v>7</v>
+      </c>
+      <c r="O80" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
-        <v>146</v>
-      </c>
-      <c r="B80" t="s">
-        <v>147</v>
-      </c>
-      <c r="C80" t="s">
-        <v>26</v>
-      </c>
-      <c r="D80" t="s">
-        <v>89</v>
-      </c>
-      <c r="E80" t="s">
-        <v>10</v>
-      </c>
-      <c r="F80" t="s">
-        <v>10</v>
-      </c>
-      <c r="G80" t="s">
-        <v>10</v>
-      </c>
-      <c r="H80" t="s">
-        <v>10</v>
-      </c>
-      <c r="I80" t="s">
-        <v>10</v>
-      </c>
-      <c r="J80" t="s">
-        <v>10</v>
-      </c>
-      <c r="K80" t="s">
-        <v>14</v>
-      </c>
-      <c r="L80" t="s">
-        <v>15</v>
-      </c>
-      <c r="M80" t="s">
-        <v>111</v>
-      </c>
-      <c r="N80" t="s">
-        <v>7</v>
-      </c>
-      <c r="O80" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="81" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>186</v>
+        <v>74</v>
       </c>
       <c r="B81" t="s">
-        <v>187</v>
+        <v>97</v>
       </c>
       <c r="C81" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="D81" t="s">
         <v>89</v>
@@ -5436,22 +5451,22 @@
         <v>173</v>
       </c>
       <c r="H81" t="s">
-        <v>10</v>
+        <v>155</v>
       </c>
       <c r="I81" t="s">
         <v>10</v>
       </c>
       <c r="J81" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="K81" t="s">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="L81" t="s">
         <v>15</v>
       </c>
       <c r="M81" t="s">
-        <v>111</v>
+        <v>15</v>
       </c>
       <c r="N81" t="s">
         <v>7</v>
@@ -5459,20 +5474,19 @@
       <c r="O81" t="s">
         <v>29</v>
       </c>
-      <c r="P81"/>
-    </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>70</v>
+        <v>146</v>
       </c>
       <c r="B82" t="s">
-        <v>65</v>
+        <v>147</v>
       </c>
       <c r="C82" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D82" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="E82" t="s">
         <v>10</v>
@@ -5493,13 +5507,13 @@
         <v>10</v>
       </c>
       <c r="K82" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="L82" t="s">
         <v>15</v>
       </c>
       <c r="M82" t="s">
-        <v>15</v>
+        <v>111</v>
       </c>
       <c r="N82" t="s">
         <v>7</v>
@@ -5508,27 +5522,27 @@
         <v>12</v>
       </c>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="B83" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="C83" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D83" t="s">
         <v>89</v>
       </c>
       <c r="E83" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F83" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="G83" t="s">
-        <v>10</v>
+        <v>173</v>
       </c>
       <c r="H83" t="s">
         <v>10</v>
@@ -5540,42 +5554,43 @@
         <v>10</v>
       </c>
       <c r="K83" t="s">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="L83" t="s">
         <v>15</v>
       </c>
       <c r="M83" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="N83" t="s">
         <v>7</v>
       </c>
       <c r="O83" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="P83"/>
+    </row>
+    <row r="84" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="B84" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C84" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="D84" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="E84" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F84" t="s">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="G84" t="s">
-        <v>173</v>
+        <v>10</v>
       </c>
       <c r="H84" t="s">
         <v>10</v>
@@ -5584,7 +5599,7 @@
         <v>10</v>
       </c>
       <c r="J84" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="K84" t="s">
         <v>33</v>
@@ -5599,18 +5614,18 @@
         <v>7</v>
       </c>
       <c r="O84" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="B85" t="s">
-        <v>171</v>
+        <v>194</v>
       </c>
       <c r="C85" t="s">
-        <v>101</v>
+        <v>15</v>
       </c>
       <c r="D85" t="s">
         <v>89</v>
@@ -5625,83 +5640,83 @@
         <v>10</v>
       </c>
       <c r="H85" t="s">
-        <v>155</v>
+        <v>10</v>
       </c>
       <c r="I85" t="s">
         <v>10</v>
       </c>
       <c r="J85" t="s">
+        <v>10</v>
+      </c>
+      <c r="K85" t="s">
+        <v>54</v>
+      </c>
+      <c r="L85" t="s">
+        <v>15</v>
+      </c>
+      <c r="M85" t="s">
+        <v>113</v>
+      </c>
+      <c r="N85" t="s">
+        <v>7</v>
+      </c>
+      <c r="O85" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>80</v>
+      </c>
+      <c r="B86" t="s">
+        <v>62</v>
+      </c>
+      <c r="C86" t="s">
+        <v>63</v>
+      </c>
+      <c r="D86" t="s">
+        <v>89</v>
+      </c>
+      <c r="E86" t="s">
+        <v>22</v>
+      </c>
+      <c r="F86" t="s">
+        <v>55</v>
+      </c>
+      <c r="G86" t="s">
+        <v>173</v>
+      </c>
+      <c r="H86" t="s">
+        <v>10</v>
+      </c>
+      <c r="I86" t="s">
+        <v>10</v>
+      </c>
+      <c r="J86" t="s">
         <v>30</v>
-      </c>
-      <c r="K85" t="s">
-        <v>14</v>
-      </c>
-      <c r="L85" t="s">
-        <v>15</v>
-      </c>
-      <c r="M85" t="s">
-        <v>15</v>
-      </c>
-      <c r="N85" t="s">
-        <v>7</v>
-      </c>
-      <c r="O85" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
-        <v>142</v>
-      </c>
-      <c r="B86" t="s">
-        <v>143</v>
-      </c>
-      <c r="C86" t="s">
-        <v>101</v>
-      </c>
-      <c r="D86" t="s">
-        <v>89</v>
-      </c>
-      <c r="E86" t="s">
-        <v>10</v>
-      </c>
-      <c r="F86" t="s">
-        <v>10</v>
-      </c>
-      <c r="G86" t="s">
-        <v>10</v>
-      </c>
-      <c r="H86" t="s">
-        <v>10</v>
-      </c>
-      <c r="I86" t="s">
-        <v>10</v>
-      </c>
-      <c r="J86" t="s">
-        <v>10</v>
       </c>
       <c r="K86" t="s">
         <v>33</v>
       </c>
-      <c r="L86">
-        <v>2023</v>
+      <c r="L86" t="s">
+        <v>15</v>
       </c>
       <c r="M86" t="s">
-        <v>141</v>
+        <v>15</v>
       </c>
       <c r="N86" t="s">
         <v>7</v>
       </c>
       <c r="O86" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>139</v>
+        <v>170</v>
       </c>
       <c r="B87" t="s">
-        <v>140</v>
+        <v>171</v>
       </c>
       <c r="C87" t="s">
         <v>101</v>
@@ -5719,176 +5734,270 @@
         <v>10</v>
       </c>
       <c r="H87" t="s">
-        <v>10</v>
+        <v>155</v>
       </c>
       <c r="I87" t="s">
         <v>10</v>
       </c>
       <c r="J87" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="K87" t="s">
+        <v>14</v>
+      </c>
+      <c r="L87" t="s">
+        <v>15</v>
+      </c>
+      <c r="M87" t="s">
+        <v>15</v>
+      </c>
+      <c r="N87" t="s">
+        <v>7</v>
+      </c>
+      <c r="O87" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>142</v>
+      </c>
+      <c r="B88" t="s">
+        <v>143</v>
+      </c>
+      <c r="C88" t="s">
+        <v>101</v>
+      </c>
+      <c r="D88" t="s">
+        <v>89</v>
+      </c>
+      <c r="E88" t="s">
+        <v>10</v>
+      </c>
+      <c r="F88" t="s">
+        <v>10</v>
+      </c>
+      <c r="G88" t="s">
+        <v>10</v>
+      </c>
+      <c r="H88" t="s">
+        <v>10</v>
+      </c>
+      <c r="I88" t="s">
+        <v>10</v>
+      </c>
+      <c r="J88" t="s">
+        <v>10</v>
+      </c>
+      <c r="K88" t="s">
         <v>33</v>
       </c>
-      <c r="L87">
+      <c r="L88">
         <v>2023</v>
       </c>
-      <c r="M87" t="s">
+      <c r="M88" t="s">
         <v>141</v>
       </c>
-      <c r="N87" t="s">
-        <v>7</v>
-      </c>
-      <c r="O87" t="s">
+      <c r="N88" t="s">
+        <v>7</v>
+      </c>
+      <c r="O88" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="89" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A89"/>
-      <c r="B89"/>
-      <c r="C89"/>
-      <c r="D89"/>
-      <c r="E89"/>
-      <c r="F89"/>
-      <c r="G89"/>
-      <c r="H89"/>
-      <c r="I89"/>
-      <c r="J89"/>
-      <c r="K89"/>
-      <c r="L89"/>
-      <c r="M89"/>
-      <c r="N89"/>
-      <c r="O89"/>
-      <c r="P89"/>
-    </row>
-    <row r="92" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A92"/>
-      <c r="B92"/>
-      <c r="C92"/>
-      <c r="D92"/>
-      <c r="E92"/>
-      <c r="F92"/>
-      <c r="G92"/>
-      <c r="H92"/>
-      <c r="I92"/>
-      <c r="J92"/>
-      <c r="K92"/>
-      <c r="L92"/>
-      <c r="M92"/>
-      <c r="N92"/>
-      <c r="O92"/>
-      <c r="P92"/>
-    </row>
-    <row r="97" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A97"/>
-      <c r="B97"/>
-      <c r="C97"/>
-      <c r="D97"/>
-      <c r="E97"/>
-      <c r="F97"/>
-      <c r="G97"/>
-      <c r="H97"/>
-      <c r="I97"/>
-      <c r="J97"/>
-      <c r="K97"/>
-      <c r="L97"/>
-      <c r="M97"/>
-      <c r="N97"/>
-      <c r="O97"/>
-      <c r="P97"/>
-    </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="M107" s="3"/>
-    </row>
-    <row r="117" spans="13:13" x14ac:dyDescent="0.3">
-      <c r="M117" s="3"/>
-    </row>
-    <row r="126" spans="13:13" x14ac:dyDescent="0.3">
-      <c r="M126" s="3"/>
-    </row>
-    <row r="135" spans="13:13" x14ac:dyDescent="0.3">
-      <c r="M135" s="3"/>
-    </row>
-    <row r="147" spans="13:13" x14ac:dyDescent="0.3">
-      <c r="M147" s="3"/>
-    </row>
-    <row r="156" spans="13:13" x14ac:dyDescent="0.3">
-      <c r="M156" s="3"/>
-    </row>
-    <row r="163" spans="13:13" x14ac:dyDescent="0.3">
-      <c r="M163" s="3"/>
-    </row>
-    <row r="172" spans="13:13" x14ac:dyDescent="0.3">
-      <c r="M172" s="3"/>
-    </row>
-    <row r="186" spans="13:13" x14ac:dyDescent="0.3">
-      <c r="M186" s="3"/>
-    </row>
-    <row r="263" spans="13:13" x14ac:dyDescent="0.3">
-      <c r="M263" s="3"/>
-    </row>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="390" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C390" s="1"/>
-    </row>
-    <row r="417" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C417" s="1"/>
-    </row>
-    <row r="420" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C420" s="1"/>
-    </row>
-    <row r="422" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>139</v>
+      </c>
+      <c r="B89" t="s">
+        <v>140</v>
+      </c>
+      <c r="C89" t="s">
+        <v>101</v>
+      </c>
+      <c r="D89" t="s">
+        <v>89</v>
+      </c>
+      <c r="E89" t="s">
+        <v>10</v>
+      </c>
+      <c r="F89" t="s">
+        <v>10</v>
+      </c>
+      <c r="G89" t="s">
+        <v>10</v>
+      </c>
+      <c r="H89" t="s">
+        <v>10</v>
+      </c>
+      <c r="I89" t="s">
+        <v>10</v>
+      </c>
+      <c r="J89" t="s">
+        <v>10</v>
+      </c>
+      <c r="K89" t="s">
+        <v>33</v>
+      </c>
+      <c r="L89">
+        <v>2023</v>
+      </c>
+      <c r="M89" t="s">
+        <v>141</v>
+      </c>
+      <c r="N89" t="s">
+        <v>7</v>
+      </c>
+      <c r="O89" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A91"/>
+      <c r="B91"/>
+      <c r="C91"/>
+      <c r="D91"/>
+      <c r="E91"/>
+      <c r="F91"/>
+      <c r="G91"/>
+      <c r="H91"/>
+      <c r="I91"/>
+      <c r="J91"/>
+      <c r="K91"/>
+      <c r="L91"/>
+      <c r="M91"/>
+      <c r="N91"/>
+      <c r="O91"/>
+      <c r="P91"/>
+    </row>
+    <row r="94" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A94"/>
+      <c r="B94"/>
+      <c r="C94"/>
+      <c r="D94"/>
+      <c r="E94"/>
+      <c r="F94"/>
+      <c r="G94"/>
+      <c r="H94"/>
+      <c r="I94"/>
+      <c r="J94"/>
+      <c r="K94"/>
+      <c r="L94"/>
+      <c r="M94"/>
+      <c r="N94"/>
+      <c r="O94"/>
+      <c r="P94"/>
+    </row>
+    <row r="99" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A99"/>
+      <c r="B99"/>
+      <c r="C99"/>
+      <c r="D99"/>
+      <c r="E99"/>
+      <c r="F99"/>
+      <c r="G99"/>
+      <c r="H99"/>
+      <c r="I99"/>
+      <c r="J99"/>
+      <c r="K99"/>
+      <c r="L99"/>
+      <c r="M99"/>
+      <c r="N99"/>
+      <c r="O99"/>
+      <c r="P99"/>
+    </row>
+    <row r="109" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M109" s="3"/>
+    </row>
+    <row r="119" spans="13:13" x14ac:dyDescent="0.35">
+      <c r="M119" s="3"/>
+    </row>
+    <row r="128" spans="13:13" x14ac:dyDescent="0.35">
+      <c r="M128" s="3"/>
+    </row>
+    <row r="137" spans="13:13" x14ac:dyDescent="0.35">
+      <c r="M137" s="3"/>
+    </row>
+    <row r="149" spans="13:13" x14ac:dyDescent="0.35">
+      <c r="M149" s="3"/>
+    </row>
+    <row r="158" spans="13:13" x14ac:dyDescent="0.35">
+      <c r="M158" s="3"/>
+    </row>
+    <row r="165" spans="13:13" x14ac:dyDescent="0.35">
+      <c r="M165" s="3"/>
+    </row>
+    <row r="174" spans="13:13" x14ac:dyDescent="0.35">
+      <c r="M174" s="3"/>
+    </row>
+    <row r="188" spans="13:13" x14ac:dyDescent="0.35">
+      <c r="M188" s="3"/>
+    </row>
+    <row r="265" spans="13:13" x14ac:dyDescent="0.35">
+      <c r="M265" s="3"/>
+    </row>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="392" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C392" s="1"/>
+    </row>
+    <row r="419" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C419" s="1"/>
+    </row>
+    <row r="422" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C422" s="1"/>
     </row>
-    <row r="433" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C433" s="1"/>
-    </row>
-    <row r="436" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C436" s="1"/>
-    </row>
-    <row r="438" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="424" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C424" s="1"/>
+    </row>
+    <row r="435" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C435" s="1"/>
+    </row>
+    <row r="438" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C438" s="1"/>
     </row>
-    <row r="449" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C449" s="1"/>
-    </row>
-    <row r="452" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C452" s="1"/>
-    </row>
-    <row r="454" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="440" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C440" s="1"/>
+    </row>
+    <row r="451" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C451" s="1"/>
+    </row>
+    <row r="454" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C454" s="1"/>
     </row>
-    <row r="460" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="E460" s="1"/>
-    </row>
-    <row r="469" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E469" s="1"/>
-    </row>
-    <row r="470" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E470" s="1"/>
-    </row>
-    <row r="487" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C487" s="1"/>
-    </row>
-    <row r="498" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C498" s="1"/>
-    </row>
-    <row r="501" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C501" s="1"/>
+    <row r="456" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C456" s="1"/>
+    </row>
+    <row r="462" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="E462" s="1"/>
+    </row>
+    <row r="471" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E471" s="1"/>
+    </row>
+    <row r="472" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E472" s="1"/>
+    </row>
+    <row r="489" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C489" s="1"/>
+    </row>
+    <row r="500" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C500" s="1"/>
+    </row>
+    <row r="503" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C503" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P512" xr:uid="{5694E675-77F6-4F54-A793-A54451BF0049}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P501">
-      <sortCondition ref="A1:A512"/>
+  <autoFilter ref="A1:P514" xr:uid="{5694E675-77F6-4F54-A793-A54451BF0049}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P503">
+      <sortCondition ref="A1:A514"/>
     </sortState>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P87">
-    <sortCondition ref="A1:A87"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P89">
+    <sortCondition ref="A1:A89"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="O57:O82 O85:O94 O1:O47">
+  <conditionalFormatting sqref="O59:O84 O87:O96 O1:O48">
     <cfRule type="containsText" dxfId="63" priority="9" operator="containsText" text="CALC">
       <formula>NOT(ISERROR(SEARCH("CALC",O1)))</formula>
     </cfRule>
@@ -5902,93 +6011,93 @@
       <formula>NOT(ISERROR(SEARCH("YES",O1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O96:O396 O399:O511 O48:P56 O95:P95 P161 P180 P263 O266:P267 P280 P287 P317 P322 P327 O345:P345 P361:P363 P385 P395 O397:P398 P399 P512 O513:O1048576">
+  <conditionalFormatting sqref="O98:O398 O401:O513 O49:P58 O97:P97 P163 P182 P265 O268:P269 P282 P289 P319 P324 P329 O347:P347 P363:P365 P387 P397 O399:P400 P401 P514 O515:O1048576">
     <cfRule type="containsText" dxfId="59" priority="841" operator="containsText" text="CALC">
-      <formula>NOT(ISERROR(SEARCH("CALC",O48)))</formula>
+      <formula>NOT(ISERROR(SEARCH("CALC",O49)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O173:O174">
+  <conditionalFormatting sqref="O175:O176">
     <cfRule type="containsText" dxfId="58" priority="581" operator="containsText" text="CALC">
-      <formula>NOT(ISERROR(SEARCH("CALC",O173)))</formula>
+      <formula>NOT(ISERROR(SEARCH("CALC",O175)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="57" priority="582" operator="containsText" text="USER">
-      <formula>NOT(ISERROR(SEARCH("USER",O173)))</formula>
+      <formula>NOT(ISERROR(SEARCH("USER",O175)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="56" priority="583" operator="containsText" text="NO">
-      <formula>NOT(ISERROR(SEARCH("NO",O173)))</formula>
+      <formula>NOT(ISERROR(SEARCH("NO",O175)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="55" priority="584" operator="containsText" text="YES">
-      <formula>NOT(ISERROR(SEARCH("YES",O173)))</formula>
+      <formula>NOT(ISERROR(SEARCH("YES",O175)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O176:O179">
+  <conditionalFormatting sqref="O178:O181">
     <cfRule type="containsText" dxfId="54" priority="465" operator="containsText" text="CALC">
-      <formula>NOT(ISERROR(SEARCH("CALC",O176)))</formula>
+      <formula>NOT(ISERROR(SEARCH("CALC",O178)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="53" priority="466" operator="containsText" text="USER">
-      <formula>NOT(ISERROR(SEARCH("USER",O176)))</formula>
+      <formula>NOT(ISERROR(SEARCH("USER",O178)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="52" priority="467" operator="containsText" text="NO">
-      <formula>NOT(ISERROR(SEARCH("NO",O176)))</formula>
+      <formula>NOT(ISERROR(SEARCH("NO",O178)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="51" priority="468" operator="containsText" text="YES">
-      <formula>NOT(ISERROR(SEARCH("YES",O176)))</formula>
+      <formula>NOT(ISERROR(SEARCH("YES",O178)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O436">
+  <conditionalFormatting sqref="O438">
     <cfRule type="containsText" dxfId="50" priority="677" operator="containsText" text="CALC">
-      <formula>NOT(ISERROR(SEARCH("CALC",O436)))</formula>
+      <formula>NOT(ISERROR(SEARCH("CALC",O438)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="49" priority="678" operator="containsText" text="USER">
-      <formula>NOT(ISERROR(SEARCH("USER",O436)))</formula>
+      <formula>NOT(ISERROR(SEARCH("USER",O438)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="48" priority="679" operator="containsText" text="NO">
-      <formula>NOT(ISERROR(SEARCH("NO",O436)))</formula>
+      <formula>NOT(ISERROR(SEARCH("NO",O438)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="47" priority="680" operator="containsText" text="YES">
-      <formula>NOT(ISERROR(SEARCH("YES",O436)))</formula>
+      <formula>NOT(ISERROR(SEARCH("YES",O438)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O501">
+  <conditionalFormatting sqref="O503">
     <cfRule type="containsText" dxfId="46" priority="313" operator="containsText" text="CALC">
-      <formula>NOT(ISERROR(SEARCH("CALC",O501)))</formula>
+      <formula>NOT(ISERROR(SEARCH("CALC",O503)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="45" priority="314" operator="containsText" text="USER">
-      <formula>NOT(ISERROR(SEARCH("USER",O501)))</formula>
+      <formula>NOT(ISERROR(SEARCH("USER",O503)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="44" priority="315" operator="containsText" text="NO">
-      <formula>NOT(ISERROR(SEARCH("NO",O501)))</formula>
+      <formula>NOT(ISERROR(SEARCH("NO",O503)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="43" priority="316" operator="containsText" text="YES">
-      <formula>NOT(ISERROR(SEARCH("YES",O501)))</formula>
+      <formula>NOT(ISERROR(SEARCH("YES",O503)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O48:P56 O95:P95 O96:O396 P161 P180 P263 O266:P267 P280 P287 P317 P322 P327 O345:P345 P361:P363 P385 P395 O397:P398 P399 O399:O511 P512 O513:O1048576">
+  <conditionalFormatting sqref="O49:P58 O97:P97 O98:O398 P163 P182 P265 O268:P269 P282 P289 P319 P324 P329 O347:P347 P363:P365 P387 P397 O399:P400 P401 O401:O513 P514 O515:O1048576">
     <cfRule type="containsText" dxfId="42" priority="842" operator="containsText" text="USER">
-      <formula>NOT(ISERROR(SEARCH("USER",O48)))</formula>
+      <formula>NOT(ISERROR(SEARCH("USER",O49)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="41" priority="843" operator="containsText" text="NO">
-      <formula>NOT(ISERROR(SEARCH("NO",O48)))</formula>
+      <formula>NOT(ISERROR(SEARCH("NO",O49)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="40" priority="844" operator="containsText" text="YES">
-      <formula>NOT(ISERROR(SEARCH("YES",O48)))</formula>
+      <formula>NOT(ISERROR(SEARCH("YES",O49)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O83:P84">
+  <conditionalFormatting sqref="O85:P86">
     <cfRule type="containsText" dxfId="39" priority="5" operator="containsText" text="CALC">
-      <formula>NOT(ISERROR(SEARCH("CALC",O83)))</formula>
+      <formula>NOT(ISERROR(SEARCH("CALC",O85)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="38" priority="6" operator="containsText" text="USER">
-      <formula>NOT(ISERROR(SEARCH("USER",O83)))</formula>
+      <formula>NOT(ISERROR(SEARCH("USER",O85)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="37" priority="7" operator="containsText" text="NO">
-      <formula>NOT(ISERROR(SEARCH("NO",O83)))</formula>
+      <formula>NOT(ISERROR(SEARCH("NO",O85)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="36" priority="8" operator="containsText" text="YES">
-      <formula>NOT(ISERROR(SEARCH("YES",O83)))</formula>
+      <formula>NOT(ISERROR(SEARCH("YES",O85)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P28:P47">
+  <conditionalFormatting sqref="P28:P48">
     <cfRule type="containsText" dxfId="35" priority="37" operator="containsText" text="CALC">
       <formula>NOT(ISERROR(SEARCH("CALC",P28)))</formula>
     </cfRule>
@@ -6002,114 +6111,114 @@
       <formula>NOT(ISERROR(SEARCH("YES",P28)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P47">
+  <conditionalFormatting sqref="P48">
     <cfRule type="containsText" dxfId="31" priority="97" operator="containsText" text="CALC">
-      <formula>NOT(ISERROR(SEARCH("CALC",P47)))</formula>
+      <formula>NOT(ISERROR(SEARCH("CALC",P48)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="30" priority="98" operator="containsText" text="USER">
-      <formula>NOT(ISERROR(SEARCH("USER",P47)))</formula>
+      <formula>NOT(ISERROR(SEARCH("USER",P48)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="29" priority="99" operator="containsText" text="NO">
-      <formula>NOT(ISERROR(SEARCH("NO",P47)))</formula>
+      <formula>NOT(ISERROR(SEARCH("NO",P48)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="28" priority="100" operator="containsText" text="YES">
-      <formula>NOT(ISERROR(SEARCH("YES",P47)))</formula>
+      <formula>NOT(ISERROR(SEARCH("YES",P48)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="27" priority="101" operator="containsText" text="CALC">
-      <formula>NOT(ISERROR(SEARCH("CALC",P47)))</formula>
+      <formula>NOT(ISERROR(SEARCH("CALC",P48)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="26" priority="102" operator="containsText" text="USER">
-      <formula>NOT(ISERROR(SEARCH("USER",P47)))</formula>
+      <formula>NOT(ISERROR(SEARCH("USER",P48)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="25" priority="103" operator="containsText" text="NO">
-      <formula>NOT(ISERROR(SEARCH("NO",P47)))</formula>
+      <formula>NOT(ISERROR(SEARCH("NO",P48)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="24" priority="104" operator="containsText" text="YES">
-      <formula>NOT(ISERROR(SEARCH("YES",P47)))</formula>
+      <formula>NOT(ISERROR(SEARCH("YES",P48)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P167">
+  <conditionalFormatting sqref="P169">
     <cfRule type="containsText" dxfId="23" priority="597" operator="containsText" text="CALC">
-      <formula>NOT(ISERROR(SEARCH("CALC",P167)))</formula>
+      <formula>NOT(ISERROR(SEARCH("CALC",P169)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="22" priority="598" operator="containsText" text="USER">
-      <formula>NOT(ISERROR(SEARCH("USER",P167)))</formula>
+      <formula>NOT(ISERROR(SEARCH("USER",P169)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="21" priority="599" operator="containsText" text="NO">
-      <formula>NOT(ISERROR(SEARCH("NO",P167)))</formula>
+      <formula>NOT(ISERROR(SEARCH("NO",P169)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="20" priority="600" operator="containsText" text="YES">
-      <formula>NOT(ISERROR(SEARCH("YES",P167)))</formula>
+      <formula>NOT(ISERROR(SEARCH("YES",P169)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P184:P187">
+  <conditionalFormatting sqref="P186:P189">
     <cfRule type="containsText" dxfId="19" priority="833" operator="containsText" text="CALC">
-      <formula>NOT(ISERROR(SEARCH("CALC",P184)))</formula>
+      <formula>NOT(ISERROR(SEARCH("CALC",P186)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="18" priority="834" operator="containsText" text="USER">
-      <formula>NOT(ISERROR(SEARCH("USER",P184)))</formula>
+      <formula>NOT(ISERROR(SEARCH("USER",P186)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="17" priority="835" operator="containsText" text="NO">
-      <formula>NOT(ISERROR(SEARCH("NO",P184)))</formula>
+      <formula>NOT(ISERROR(SEARCH("NO",P186)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="16" priority="836" operator="containsText" text="YES">
-      <formula>NOT(ISERROR(SEARCH("YES",P184)))</formula>
+      <formula>NOT(ISERROR(SEARCH("YES",P186)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P230:P231">
+  <conditionalFormatting sqref="P232:P233">
     <cfRule type="containsText" dxfId="15" priority="517" operator="containsText" text="CALC">
-      <formula>NOT(ISERROR(SEARCH("CALC",P230)))</formula>
+      <formula>NOT(ISERROR(SEARCH("CALC",P232)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="14" priority="518" operator="containsText" text="USER">
-      <formula>NOT(ISERROR(SEARCH("USER",P230)))</formula>
+      <formula>NOT(ISERROR(SEARCH("USER",P232)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="13" priority="519" operator="containsText" text="NO">
-      <formula>NOT(ISERROR(SEARCH("NO",P230)))</formula>
+      <formula>NOT(ISERROR(SEARCH("NO",P232)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="12" priority="520" operator="containsText" text="YES">
-      <formula>NOT(ISERROR(SEARCH("YES",P230)))</formula>
+      <formula>NOT(ISERROR(SEARCH("YES",P232)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P265 P269:P270">
+  <conditionalFormatting sqref="P267 P271:P272">
     <cfRule type="containsText" dxfId="11" priority="233" operator="containsText" text="CALC">
-      <formula>NOT(ISERROR(SEARCH("CALC",P265)))</formula>
+      <formula>NOT(ISERROR(SEARCH("CALC",P267)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="10" priority="234" operator="containsText" text="USER">
-      <formula>NOT(ISERROR(SEARCH("USER",P265)))</formula>
+      <formula>NOT(ISERROR(SEARCH("USER",P267)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="9" priority="235" operator="containsText" text="NO">
-      <formula>NOT(ISERROR(SEARCH("NO",P265)))</formula>
+      <formula>NOT(ISERROR(SEARCH("NO",P267)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="8" priority="236" operator="containsText" text="YES">
-      <formula>NOT(ISERROR(SEARCH("YES",P265)))</formula>
+      <formula>NOT(ISERROR(SEARCH("YES",P267)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P339 O344 P350">
+  <conditionalFormatting sqref="P341 O346 P352">
     <cfRule type="containsText" dxfId="7" priority="829" operator="containsText" text="CALC">
-      <formula>NOT(ISERROR(SEARCH("CALC",O339)))</formula>
+      <formula>NOT(ISERROR(SEARCH("CALC",O341)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="6" priority="830" operator="containsText" text="USER">
-      <formula>NOT(ISERROR(SEARCH("USER",O339)))</formula>
+      <formula>NOT(ISERROR(SEARCH("USER",O341)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="5" priority="831" operator="containsText" text="NO">
-      <formula>NOT(ISERROR(SEARCH("NO",O339)))</formula>
+      <formula>NOT(ISERROR(SEARCH("NO",O341)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="4" priority="832" operator="containsText" text="YES">
-      <formula>NOT(ISERROR(SEARCH("YES",O339)))</formula>
+      <formula>NOT(ISERROR(SEARCH("YES",O341)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P421:P424">
+  <conditionalFormatting sqref="P423:P426">
     <cfRule type="containsText" dxfId="3" priority="737" operator="containsText" text="CALC">
-      <formula>NOT(ISERROR(SEARCH("CALC",P421)))</formula>
+      <formula>NOT(ISERROR(SEARCH("CALC",P423)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="2" priority="738" operator="containsText" text="USER">
-      <formula>NOT(ISERROR(SEARCH("USER",P421)))</formula>
+      <formula>NOT(ISERROR(SEARCH("USER",P423)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="1" priority="739" operator="containsText" text="NO">
-      <formula>NOT(ISERROR(SEARCH("NO",P421)))</formula>
+      <formula>NOT(ISERROR(SEARCH("NO",P423)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="0" priority="740" operator="containsText" text="YES">
-      <formula>NOT(ISERROR(SEARCH("YES",P421)))</formula>
+      <formula>NOT(ISERROR(SEARCH("YES",P423)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
